--- a/cases/orbit_catalog.xlsx
+++ b/cases/orbit_catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_75A9A810140279A5085C1732C514727C7CEDF480" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CC7E26-BCB4-41F3-B6C0-36930FC958AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="orbit_catalog" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="41">
   <si>
     <t>no</t>
   </si>
@@ -62,18 +62,6 @@
   </si>
   <si>
     <t>orbit_period_s</t>
-  </si>
-  <si>
-    <t>eclipse_entry_time_s</t>
-  </si>
-  <si>
-    <t>eclipse_exit_time_s</t>
-  </si>
-  <si>
-    <t>eclipse_duration_s</t>
-  </si>
-  <si>
-    <t>sunlit_duration_s</t>
   </si>
   <si>
     <t>notes</t>
@@ -218,7 +206,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -391,11 +379,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -465,6 +462,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -746,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -763,7 +763,7 @@
     <col min="13" max="13" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="43.5" customHeight="1" thickBot="1">
+    <row r="1" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -803,31 +803,19 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="29.25" customHeight="1" thickBot="1">
+    </row>
+    <row r="2" spans="1:14" ht="29.25" customHeight="1" thickBot="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D2" s="7">
         <v>97.8</v>
@@ -836,7 +824,7 @@
         <v>270</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G2" s="7">
         <v>600</v>
@@ -854,19 +842,19 @@
         <v>2.3800000000000001E-4</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="R2" s="8"/>
-    </row>
-    <row r="3" spans="1:18" ht="43.5" customHeight="1" thickBot="1">
+        <v>17</v>
+      </c>
+      <c r="N2" s="8"/>
+    </row>
+    <row r="3" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D3" s="12">
         <v>97.8</v>
@@ -875,7 +863,7 @@
         <v>270</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G3" s="12">
         <v>600</v>
@@ -893,19 +881,19 @@
         <v>1.8900000000000001E-4</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R3" s="13"/>
-    </row>
-    <row r="4" spans="1:18" ht="43.5" customHeight="1" thickBot="1">
+        <v>17</v>
+      </c>
+      <c r="N3" s="13"/>
+    </row>
+    <row r="4" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4" s="7">
         <v>97.8</v>
@@ -914,7 +902,7 @@
         <v>270</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G4" s="7">
         <v>600</v>
@@ -932,19 +920,19 @@
         <v>2.61E-4</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="R4" s="8"/>
-    </row>
-    <row r="5" spans="1:18" ht="29.25" customHeight="1" thickBot="1">
+        <v>17</v>
+      </c>
+      <c r="N4" s="8"/>
+    </row>
+    <row r="5" spans="1:14" ht="29.25" customHeight="1" thickBot="1">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D5" s="12">
         <v>98.64</v>
@@ -953,7 +941,7 @@
         <v>270</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G5" s="12">
         <v>800</v>
@@ -971,19 +959,19 @@
         <v>2.3800000000000001E-4</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R5" s="13"/>
-    </row>
-    <row r="6" spans="1:18" ht="43.5" customHeight="1" thickBot="1">
+        <v>17</v>
+      </c>
+      <c r="N5" s="13"/>
+    </row>
+    <row r="6" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D6" s="7">
         <v>98.64</v>
@@ -992,7 +980,7 @@
         <v>270</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G6" s="7">
         <v>800</v>
@@ -1010,19 +998,19 @@
         <v>1.8900000000000001E-4</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="R6" s="8"/>
-    </row>
-    <row r="7" spans="1:18" ht="43.5" customHeight="1" thickBot="1">
+        <v>17</v>
+      </c>
+      <c r="N6" s="8"/>
+    </row>
+    <row r="7" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A7" s="9">
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D7" s="12">
         <v>98.64</v>
@@ -1031,7 +1019,7 @@
         <v>270</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G7" s="12">
         <v>800</v>
@@ -1049,19 +1037,19 @@
         <v>2.61E-4</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R7" s="13"/>
-    </row>
-    <row r="8" spans="1:18" ht="43.5" customHeight="1" thickBot="1">
+        <v>17</v>
+      </c>
+      <c r="N7" s="13"/>
+    </row>
+    <row r="8" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D8" s="7">
         <v>97.817999999999998</v>
@@ -1088,21 +1076,21 @@
         <v>2.3800000000000001E-4</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R8" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="43.5" customHeight="1" thickBot="1">
+        <v>24</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A9" s="9">
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D9" s="12">
         <v>97.817999999999998</v>
@@ -1129,21 +1117,21 @@
         <v>1.8900000000000001E-4</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="R9" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="43.5" customHeight="1" thickBot="1">
+        <v>24</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D10" s="7">
         <v>98.632999999999996</v>
@@ -1170,21 +1158,24 @@
         <v>1.8900000000000001E-4</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R10" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="29.25" customHeight="1" thickBot="1">
+        <v>24</v>
+      </c>
+      <c r="M10" s="24">
+        <v>6052</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="29.25" customHeight="1" thickBot="1">
       <c r="A11" s="9">
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D11" s="12">
         <v>97.4</v>
@@ -1193,7 +1184,7 @@
         <v>285</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G11" s="12">
         <v>500</v>
@@ -1211,19 +1202,19 @@
         <v>2.3800000000000001E-4</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R11" s="13"/>
-    </row>
-    <row r="12" spans="1:18" ht="43.5" customHeight="1" thickBot="1">
+        <v>17</v>
+      </c>
+      <c r="N11" s="13"/>
+    </row>
+    <row r="12" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D12" s="7">
         <v>97.385999999999996</v>
@@ -1250,21 +1241,21 @@
         <v>1.8900000000000001E-4</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R12" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="57.75" customHeight="1" thickBot="1">
+        <v>24</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="57.75" customHeight="1" thickBot="1">
       <c r="A13" s="9">
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D13" s="12">
         <v>97.385999999999996</v>
@@ -1291,21 +1282,21 @@
         <v>2.3800000000000001E-4</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="R13" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="43.5" customHeight="1" thickBot="1">
+        <v>24</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="43.5" customHeight="1" thickBot="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D14" s="7">
         <v>98.64</v>
@@ -1314,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G14" s="7">
         <v>800</v>
@@ -1332,19 +1323,19 @@
         <v>1.8900000000000001E-4</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R14" s="8"/>
-    </row>
-    <row r="15" spans="1:18" ht="60.75" customHeight="1" thickBot="1">
+        <v>32</v>
+      </c>
+      <c r="N14" s="8"/>
+    </row>
+    <row r="15" spans="1:14" ht="60.75" customHeight="1" thickBot="1">
       <c r="A15" s="18">
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D15" s="12">
         <v>97.8</v>
@@ -1353,7 +1344,7 @@
         <v>270</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G15" s="12">
         <v>600</v>
@@ -1371,21 +1362,21 @@
         <v>2.3800000000000001E-4</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R15" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="60.75" customHeight="1" thickBot="1">
+        <v>17</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="60.75" customHeight="1" thickBot="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D16" s="7">
         <v>97.8</v>
@@ -1394,7 +1385,7 @@
         <v>270</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G16" s="7">
         <v>600</v>
@@ -1412,21 +1403,21 @@
         <v>1.8900000000000001E-4</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="60.75" customHeight="1" thickBot="1">
+        <v>17</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="60.75" customHeight="1" thickBot="1">
       <c r="A17" s="9">
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D17" s="12">
         <v>97.817999999999998</v>
@@ -1453,21 +1444,21 @@
         <v>1.8900000000000001E-4</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="R17" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="60.75" customHeight="1" thickBot="1">
+        <v>24</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="60.75" customHeight="1" thickBot="1">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D18" s="7">
         <v>98.632999999999996</v>
@@ -1494,21 +1485,21 @@
         <v>1.8900000000000001E-4</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="60.75" customHeight="1" thickBot="1">
+        <v>24</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="60.75" customHeight="1" thickBot="1">
       <c r="A19" s="9">
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D19" s="12">
         <v>97.385999999999996</v>
@@ -1535,21 +1526,21 @@
         <v>1.8900000000000001E-4</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="R19" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="60.75" customHeight="1" thickBot="1">
+        <v>24</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="60.75" customHeight="1" thickBot="1">
       <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D20" s="7">
         <v>97.385999999999996</v>
@@ -1576,21 +1567,21 @@
         <v>2.3800000000000001E-4</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R20" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="60.75" customHeight="1" thickBot="1">
+        <v>24</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="60.75" customHeight="1" thickBot="1">
       <c r="A21" s="19">
         <v>20</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D21" s="22">
         <v>98.64</v>
@@ -1599,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G21" s="22">
         <v>800</v>
@@ -1617,10 +1608,10 @@
         <v>1.8900000000000001E-4</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="R21" s="23" t="s">
-        <v>38</v>
+        <v>32</v>
+      </c>
+      <c r="N21" s="23" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/cases/orbit_catalog.xlsx
+++ b/cases/orbit_catalog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="orbit_catalog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="orbit_catalog_archive" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="orbit_catalog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="orbit_catalog_archive" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51,7 +51,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -59,14 +59,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -434,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,6 +623,31 @@
           <t>notes_attitude</t>
         </is>
       </c>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t>pat_orbit_error_frame</t>
+        </is>
+      </c>
+      <c r="AK1" s="2" t="inlineStr">
+        <is>
+          <t>orbit_error_stt_frame</t>
+        </is>
+      </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t>orbit_error_partner_mode</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t>orbit_error_stt_status</t>
+        </is>
+      </c>
+      <c r="AN1" s="2" t="inlineStr">
+        <is>
+          <t>orbit_error_stt_notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -754,6 +789,31 @@
           <t>constraint_target=velocity. eff_velocity_face / eff_nadir_face are always both filled: the constrained one has source=constraint, the other source=effective (velocity×sun triad third when velocity is constrained; sign chosen so |β|~90° → nadir not zenith).</t>
         </is>
       </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight_cyclic</t>
+        </is>
+      </c>
+      <c r="AK2" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight</t>
+        </is>
+      </c>
+      <c r="AL2" s="4" t="inlineStr">
+        <is>
+          <t>zenith_proxy</t>
+        </is>
+      </c>
+      <c r="AM2" s="4" t="inlineStr">
+        <is>
+          <t>ready_unrealistic_link</t>
+        </is>
+      </c>
+      <c r="AN2" s="4" t="inlineStr">
+        <is>
+          <t>LCT~zenith; angle math OK but not a realistic Earth/ISL link</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +955,31 @@
           <t>constraint_target=velocity. eff_velocity_face / eff_nadir_face are always both filled: the constrained one has source=constraint, the other source=effective (velocity×sun triad third when velocity is constrained; sign chosen so |β|~90° → nadir not zenith).</t>
         </is>
       </c>
+      <c r="AJ3" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight_cyclic</t>
+        </is>
+      </c>
+      <c r="AK3" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight</t>
+        </is>
+      </c>
+      <c r="AL3" s="4" t="inlineStr">
+        <is>
+          <t>isl_along_track</t>
+        </is>
+      </c>
+      <c r="AM3" s="4" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="AN3" s="4" t="inlineStr">
+        <is>
+          <t>LCT~along-track; ISL range=800 km</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1121,23 @@
           <t>constraint_target=velocity. eff_velocity_face / eff_nadir_face are always both filled: the constrained one has source=constraint, the other source=effective (velocity×sun triad third when velocity is constrained; sign chosen so |β|~90° → nadir not zenith).</t>
         </is>
       </c>
+      <c r="AJ4" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight_cyclic</t>
+        </is>
+      </c>
+      <c r="AK4" s="4" t="inlineStr"/>
+      <c r="AL4" s="4" t="inlineStr"/>
+      <c r="AM4" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="AN4" s="4" t="inlineStr">
+        <is>
+          <t>not in bcase set / not run</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1177,6 +1279,31 @@
           <t>constraint_target=velocity. eff_velocity_face / eff_nadir_face are always both filled: the constrained one has source=constraint, the other source=effective (velocity×sun triad third when velocity is constrained; sign chosen so |β|~90° → nadir not zenith).</t>
         </is>
       </c>
+      <c r="AJ5" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight_cyclic</t>
+        </is>
+      </c>
+      <c r="AK5" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight</t>
+        </is>
+      </c>
+      <c r="AL5" s="4" t="inlineStr">
+        <is>
+          <t>ground_nadir</t>
+        </is>
+      </c>
+      <c r="AM5" s="4" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="AN5" s="4" t="inlineStr">
+        <is>
+          <t>LCT~nadir; ground range~altitude=695 km</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1318,6 +1445,31 @@
           <t>constraint_target=velocity. eff_velocity_face / eff_nadir_face are always both filled: the constrained one has source=constraint, the other source=effective (velocity×sun triad third when velocity is constrained; sign chosen so |β|~90° → nadir not zenith).</t>
         </is>
       </c>
+      <c r="AJ6" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight_cyclic</t>
+        </is>
+      </c>
+      <c r="AK6" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight</t>
+        </is>
+      </c>
+      <c r="AL6" s="4" t="inlineStr">
+        <is>
+          <t>isl_along_track</t>
+        </is>
+      </c>
+      <c r="AM6" s="4" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="AN6" s="4" t="inlineStr">
+        <is>
+          <t>LCT~anti-along-track; ISL range=800 km</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1459,6 +1611,31 @@
           <t>constraint_target=velocity. eff_velocity_face / eff_nadir_face are always both filled: the constrained one has source=constraint, the other source=effective (velocity×sun triad third when velocity is constrained; sign chosen so |β|~90° → nadir not zenith).</t>
         </is>
       </c>
+      <c r="AJ7" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight_cyclic</t>
+        </is>
+      </c>
+      <c r="AK7" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight</t>
+        </is>
+      </c>
+      <c r="AL7" s="4" t="inlineStr">
+        <is>
+          <t>isl_along_track</t>
+        </is>
+      </c>
+      <c r="AM7" s="4" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="AN7" s="4" t="inlineStr">
+        <is>
+          <t>LCT~along-track; ISL range=800 km</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1594,6 +1771,31 @@
       <c r="AI8" s="4" t="inlineStr">
         <is>
           <t>constraint_target=velocity. eff_velocity_face / eff_nadir_face are always both filled: the constrained one has source=constraint, the other source=effective (velocity×sun triad third when velocity is constrained; sign chosen so |β|~90° → nadir not zenith).</t>
+        </is>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight_cyclic</t>
+        </is>
+      </c>
+      <c r="AK8" s="4" t="inlineStr">
+        <is>
+          <t>stt_body_lct_boresight</t>
+        </is>
+      </c>
+      <c r="AL8" s="4" t="inlineStr">
+        <is>
+          <t>isl_along_track</t>
+        </is>
+      </c>
+      <c r="AM8" s="4" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="AN8" s="4" t="inlineStr">
+        <is>
+          <t>LCT~along-track; ISL range=800 km</t>
         </is>
       </c>
     </row>
@@ -1612,72 +1814,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>td_orbit_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>orbit_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>inclination_deg</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>raan_deg</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>epoch_utc</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>min_alt_km</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>max_alt_km</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>solar_w_per_mm2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>albedo</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ir_w_per_mm2</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>illumination_condition</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>orbit_period_s</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
